--- a/港岛-坚尼地城及摩星岭-海嵎/海嵎_销控明细表.xlsx
+++ b/港岛-坚尼地城及摩星岭-海嵎/海嵎_销控明细表.xlsx
@@ -1533,23 +1533,19 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>10017000</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>34781</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1558,12 +1554,12 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1573,7 +1569,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -9125,7 +9121,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -9135,7 +9131,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>111</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -9348,12 +9344,12 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
-招标单位
--
-(在售)</t>
+$1002万
+$34,781/呎
+(26年-09月-06日)</t>
         </is>
       </c>
     </row>

--- a/港岛-坚尼地城及摩星岭-海嵎/海嵎_销控明细表.xlsx
+++ b/港岛-坚尼地城及摩星岭-海嵎/海嵎_销控明细表.xlsx
@@ -2602,7 +2602,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -9427,7 +9427,7 @@
           <t>B | 284呎 (1房)
 $1042万
 $36,687/呎
-(26年-08月-14日)</t>
+(26年-09月-08日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">

--- a/港岛-坚尼地城及摩星岭-海嵎/海嵎_销控明细表.xlsx
+++ b/港岛-坚尼地城及摩星岭-海嵎/海嵎_销控明细表.xlsx
@@ -2668,14 +2668,14 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>10313000</v>
+        <v>7650000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>35934</v>
+        <v>26655</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -9417,9 +9417,9 @@
       <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
-$1031万
-$35,934/呎
-(26年-08月-27日)</t>
+$765万
+$26,655/呎
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">

--- a/港岛-坚尼地城及摩星岭-海嵎/海嵎_销控明细表.xlsx
+++ b/港岛-坚尼地城及摩星岭-海嵎/海嵎_销控明细表.xlsx
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -9349,7 +9349,7 @@
           <t>F | 288呎 (1房)
 $1002万
 $34,781/呎
-(26年-09月-06日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
     </row>

--- a/港岛-坚尼地城及摩星岭-海嵎/海嵎_销控明细表.xlsx
+++ b/港岛-坚尼地城及摩星岭-海嵎/海嵎_销控明细表.xlsx
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -9261,7 +9261,7 @@
           <t>A | 471呎 (2房)
 $2260万
 $47,983/呎
-(26年-08月-31日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">

--- a/港岛-坚尼地城及摩星岭-海嵎/海嵎_销控明细表.xlsx
+++ b/港岛-坚尼地城及摩星岭-海嵎/海嵎_销控明细表.xlsx
@@ -1397,23 +1397,19 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>10732000</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>37789</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1422,12 +1418,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1437,7 +1433,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2668,14 +2664,14 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>7650000</v>
+        <v>10313000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>26655</v>
+        <v>35934</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -9121,7 +9117,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -9131,7 +9127,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>112</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -9264,12 +9260,12 @@
 (26年-09月-25日)</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
-招标单位
--
-(在售)</t>
+$1073万
+$37,789/呎
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -9417,9 +9413,9 @@
       <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
-$765万
-$26,655/呎
-(26年-09月-21日)</t>
+$1031万
+$35,934/呎
+(26年-08月-27日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">

--- a/港岛-坚尼地城及摩星岭-海嵎/海嵎_销控明细表.xlsx
+++ b/港岛-坚尼地城及摩星岭-海嵎/海嵎_销控明细表.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -8665,23 +8665,19 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I122" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>10040000</v>
+      </c>
+      <c r="I122" s="5" t="n">
+        <v>40000</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
@@ -8690,12 +8686,12 @@
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M122" s="3" t="inlineStr">
@@ -8705,7 +8701,7 @@
       </c>
       <c r="N122" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -9117,7 +9113,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -9127,7 +9123,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>113</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -9265,7 +9261,7 @@
           <t>B | 284呎 (1房)
 $1073万
 $37,789/呎
-(26年-09月-29日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -10330,12 +10326,12 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="G26" s="23" t="inlineStr">
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>F | 251呎 (1房)
-招标单位
--
-(在售)</t>
+$1004万
+$40,000/呎
+(26年-10月-20日)</t>
         </is>
       </c>
     </row>
